--- a/outputs/外注テスト項目書_2026-07-02.xlsx
+++ b/outputs/外注テスト項目書_2026-07-02.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B_要望確認テスト" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'A_機能テスト'!$A$1:$F$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'B_要望確認テスト'!$A$1:$H$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'A_機能テスト'!$A$1:$H$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'B_要望確認テスト'!$A$1:$H$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -32,18 +32,18 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
     </font>
   </fonts>
   <fills count="3">
@@ -87,15 +87,19 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -463,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -489,28 +493,42 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>・進め方は「外注テスト手順書」をお読みください</t>
+          <t>・実施前に必ず「外注テスト手順書」をお読みください（システムの説明・準備・記入ルール）。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>・A_機能テスト: 仕様書v2.0からランダムに選んだ確認項目（15件／乱数シード20260702で再現可能）</t>
+          <t>・シート「A_機能テスト」: システムの基本機能が仕様どおり動くかの確認（仕様書v2.0から15項目をランダムに選定。乱数シード20260702で再現可能）。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>・B_要望確認テスト: 2026-03-14以降にご報告いただいた不具合・要望の全件確認（21件）</t>
+          <t>・シート「B_要望確認テスト」: これまでにお客様から報告のあった不具合・要望が直っているかの確認（2026-03-14以降の全件）。全項目実施してください。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>・「結果」列に OK / NG を記入し、NGは備考に詳細をお願いします</t>
+          <t>・各項目は「事前準備」→「操作手順①②③…」→「期待する結果」の順に読んでください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>・「結果」欄に OK / NG を記入。NGのときは備考に「どの手順まで進んだか・何が起きたか・スクリーンショットの有無」を書いてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>・備考欄に「時間条件つき」「発生した場合のみ」「マイク使用」とある項目は、手順書の「4-1. 実施する順番」を参考にしてください。</t>
         </is>
       </c>
     </row>
@@ -525,15 +543,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -549,20 +569,30 @@
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>確認すること</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>期待結果</t>
+          <t>事前準備</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
+          <t>操作手順</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>期待する結果</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
           <t>結果(OK/NG)</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -581,16 +611,28 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>「LOGIN」を押した直後のボタンを見る</t>
+          <t>ログインボタンを押したことが見た目でわかること</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>ボタンが「Logging in...」に変わり、連打しても反応しない</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr"/>
-      <c r="F2" s="5" t="inlineStr"/>
+          <t>Chromeでテスト用URLを開き、ユーザーAのIDとパスワードを入力した状態</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>① 「LOGIN」ボタンを1回だけ押す。
+② 押した直後のボタンの見た目を観察する。
+③ 画面が切り替わる前に、もう一度ボタンを押してみる。</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>結果: ボタンの文字が「Logging in...」に変わっている。2回目に押しても反応しない（二重に処理されない）。</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr"/>
+      <c r="H2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -605,16 +647,28 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>学年・パート・サブパートのプルダウンを開く</t>
+          <t>自分の進み具合より先のステージが選べないこと</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>自分が解放しているステージまでしか表示されない（先のステージは選べない）</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr"/>
-      <c r="F3" s="5" t="inlineStr"/>
+          <t>ユーザーB（進捗が途中のアカウント）でログインした状態</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>① 「Grade」（学年）のプルダウンを開き、選べる数字をメモする。
+② 「Part」（パート）のプルダウンを開き、いちばん大きい数字をメモする。
+③ 準備シートに書かれたユーザーBの進捗（例: 学年1のパート10まで）と見比べる。</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>結果: ユーザーBの進捗より先の学年・パートはプルダウンに表示されていない。</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr"/>
+      <c r="H3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -629,16 +683,28 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>「Ranking 🏆」を押す</t>
+          <t>ランキング画面に移動して戻れること</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>ランキング画面に移動する</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
+          <t>ユーザーAでログインし、ステージ選択画面を開いた状態</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>① 画面右上の「Ranking 🏆」ボタンを押す。
+② ランキング画面が表示されたら、内容を確認する。
+③ 「Back」ボタンを押す。</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>結果: ①で「Ranking 👑」の画面に切り替わり、今月の期間（例: Period: 2026/07）と「Number of try」「Best Scores」の2つの表が表示されている。③でステージ選択画面に戻っている。</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -653,16 +719,29 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>1ステージを最後までプレイし、出題数を数える</t>
+          <t>ゲーム開始前に「回答条件」が表示されること</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>問題は全部で8問（最初の1問はデモ）出題される</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
+          <t>ユーザーAでログインし、ステージ選択画面を開いた状態</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>① Gradeで「1」、Partで「1」、Subpartで「1」を選ぶ。
+② 「Game Start」ボタンを押す。
+③ 表示された画面の内容を確認する。
+④ 「Start」ボタンを押す。</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>結果: ③で「Requirement」という見出しの白いパネルに、日本語の説明（この問題の答え方のルール）が表示されている。④でゲームが始まる。</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -677,16 +756,28 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>2問目以降で問題の音声を聞く</t>
+          <t>1ステージの問題数が8問であること</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>問題文が2回読み上げられてから回答できるようになる</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
+          <t>ユーザーAでログインした状態</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>① 好きなステージ（例: Grade1・Part1・Subpart1）を開始する。
+② 何も答えずに時間切れで進めてよいので、最後までプレイする。
+③ 画面左上の丸の中の数字（いま何問目か）を毎回確認する。</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>結果: 数字が1から8まで進み、8問目が終わると結果画面に切り替わる（合計8問）。</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -701,16 +792,28 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>2問目以降でタイマーを見る</t>
+          <t>問題の音声が2回読み上げられてから回答できること</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>30秒からカウントダウンし、残り10秒前後で赤色になる</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr"/>
+          <t>ユーザーAでログインし、音が聞こえる状態</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>① 好きなステージを開始する。
+② 2問目になったら、音声の回数を数える。
+③ 音声が終わったあと、画面下の銃のボタンが押せるようになるか確認する。</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>結果: 同じ問題文の音声が2回流れる。2回流れ終わると銃のボタンが押せるようになる。</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -725,16 +828,28 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>何も答えずに時間切れまで待つ</t>
+          <t>制限時間のカウントダウンが正しく動くこと</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>正解が音声と文字で表示され、自動で次の問題に進む（固まらない）</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="5" t="inlineStr"/>
+          <t>ユーザーAでログインした状態</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>① 好きなステージを開始し、2問目まで進める。
+② 画面左の青い丸（タイマー）を観察する。
+③ 何も答えずにそのまま見続ける。</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>結果: 30秒から1秒ずつ減っていき、残り10秒くらいになると丸が赤色に変わる。</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -749,16 +864,30 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>銃ボタンを押してマイクをONにする</t>
+          <t>マイクで正解を言うと正解の演出になること</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>右上が「🎤 MIC: ON」になり、話した内容が「Heard: …」に表示される</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr"/>
+          <t>ユーザーAでログインし、マイクが使える状態</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>① Grade1・Part1・Subpart1 を開始する。
+② 1問目（デモ）で正解の答え方のお手本を確認する。
+③ 2問目で画面下の銃のボタンを押す（マイクON）。
+④ デモと同じ要領で、画面の英文に対する答えをマイクに向かって言う（このステージは英文の主語1語が答え。例: 問題が You run fast. なら「You」）。
+⑤ もう一度銃のボタンを押す（マイクOFF＝回答確定）。</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>結果: ビームが出て敵が爆発する演出のあと、緑色のパネルに正解が表示され、次の問題に進む。</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -768,21 +897,32 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>結果</t>
+          <t>結果画面</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>同じステージを10回プレイする（クリアしなくてよい）</t>
+          <t>スコアが正しく表示されること</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>10回目のあと、次のステージが自動で解放される</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
+          <t>ユーザーAでログインした状態</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>① 好きなステージを最後まで（8問）プレイする。正解できなくてもよい。
+② 結果画面の表示内容を確認する。</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>結果: 「Your Score」に「正解数 / 7」とパーセントが表示されている（1問目はお手本なので分母は7問）。</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -792,21 +932,34 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ランキング</t>
+          <t>結果画面</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>ランキング画面を開く</t>
+          <t>「あと何問でクリア」の数が正しいこと</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>今月の「Number of try」と「Best Scores」の上位3名が表示される</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
+          <t>ユーザーAでログインした状態</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>① 好きなステージを最後までプレイする（正解数は何問でもよい）。
+② 結果画面の「Your Score」の正解数をメモする。
+③ その下の「あと N 問正解でクリア！」の N を確認する。
+④ 「5 −（正解数）＝ N」になっているか計算する（クリアは5問正解）。</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>結果: Nが「5−正解数」と一致している。例: 3問正解なら「あと2問」、0問正解なら「あと5問」。</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -816,21 +969,34 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>管理画面</t>
+          <t>結果画面</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>（先生用）名前とニックネームを入れて「登録」を押す</t>
+          <t>クリアできなくても10回挑戦すると次のステージへ進めること【時間がかかる項目・約40分】</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>新しいユーザーIDとパスワードが画面に表示される</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
+          <t>ユーザーB（進捗が途中のアカウント）でログインした状態</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>① ユーザーBの現在のステージ（プルダウンで最後に出てくるステージ）を開始する。
+② クリアせずに（答えなくてよい）最後までプレイする。※「やめる」で途中終了すると回数に数えられないので、必ず結果画面まで進めること。
+③ 「Retry」からもう一度同じステージをプレイする。これを合計10回繰り返す。
+④ 10回目の結果画面のあと、ステージ選択画面のプルダウンを確認する。</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>結果: 10回目が終わると、クリアしていなくても次のステージがプルダウンに追加されて選べるようになっている。</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -840,21 +1006,32 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>管理画面</t>
+          <t>ランキング</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>（先生用）ユーザーの「編集」で学年・パートを変えて「保存」</t>
+          <t>プレイするとランキングに反映されること</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>一覧の表示が変わり、その生徒は変更後のステージから遊べる</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="5" t="inlineStr"/>
+          <t>ユーザーAで何回かステージをプレイし終えた状態</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>① ステージ選択画面の「Ranking 🏆」を押す。
+② 「Number of try」（挑戦回数）の表を見る。</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>結果: 今月たくさんプレイした人の名前（ニックネーム）が上位3名まで表示され、自分がたくさんプレイしていれば自分のニックネームが載っている。</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -869,16 +1046,30 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>（先生用）ユーザーIDを入れて「パスワードリセット」</t>
+          <t>生徒の一覧と進捗が表示・変更できること（先生用機能）</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>新しいパスワードが表示され、そのパスワードでログインできる</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr"/>
+          <t>管理者ユーザーでログインした状態（自動で管理者画面が開く）</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>① 「ユーザー情報」の表に生徒の一覧が表示されているか確認する。
+② どれか1人の「編集」を押す。
+③ 「解いている最新のパート」の数字を1つ変えて「保存」を押す。
+④ 表の表示が変わったか確認する。
+⑤ 同じ手順で元の数字に戻しておく。</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>結果: 生徒の一覧が表示され、③の変更が④で表に反映されている。</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -888,21 +1079,34 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>全体</t>
+          <t>管理画面</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>iPadまたはiPhoneを横向きにしてプレイする</t>
+          <t>新しい生徒を登録できること（先生用機能）</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>文字やボタンがはみ出したり重なったりしない</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr"/>
+          <t>管理者ユーザーでログインした状態</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>① 「新規登録」の「名前」に「テスト 花子」、「ニックネーム」に「はなこ」と入力する。
+② 「登録」ボタンを押す。
+③ 画面に表示されたユーザーIDとパスワードをメモする。
+④ いったんログアウトし（ブラウザで再度URLを開き直してもよい）、メモしたIDとパスワードでログインしてみる。</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>結果: ③でIDとパスワードが発行され、④でその生徒としてログインできる（最初のステージだけが選べる状態）。</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -912,24 +1116,38 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>全体</t>
+          <t>管理画面</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>ゲーム中に画面が固まった場合の動きを見る（発生した場合のみ）</t>
+          <t>パスワードをリセットできること（先生用機能）</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>20秒ほどで「画面が停止しました」の画面が出て「リトライ/次の問題へ/やめる」を選べる</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
+          <t>管理者ユーザーでログインした状態</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>① 「パスワードリセット」の欄に、ユーザーBのIDを入力する。
+② 「パスワードリセット」ボタンを押す。
+③ 表示された新しいパスワードをメモする。
+④ ユーザーBのIDと「古い」パスワードでログインしてみる。
+⑤ ユーザーBのIDと「新しい」パスワードでログインしてみる。</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>結果: ④は失敗し、⑤は成功する。※実施後は藤岡へ新パスワードを共有してください。</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F16"/>
+  <autoFilter ref="A1:H16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -940,17 +1158,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -971,17 +1189,17 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>対象画面</t>
+          <t>事前準備</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>手順</t>
+          <t>操作手順</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>期待結果</t>
+          <t>期待する結果</t>
         </is>
       </c>
       <c r="G1" s="3" t="inlineStr">
@@ -1008,22 +1226,24 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>1-24/1-25の音声が出ない</t>
+          <t>1-24と1-25で音声が出ない</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>ゲーム</t>
+          <t>ユーザーAでログインし、音が聞こえる状態</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>中1のパート24-1、24-2、25-1をプレイする</t>
+          <t>① Grade「1」・Part「24」・Subpart「1」を開始する。
+② 各問題で「問題の音声」と「正解発表のときの音声」が流れるか聞く（時間切れで進めてよい）。
+③ 同じことを Part「24」Subpart「2」、Part「25」Subpart「1」でも行う。</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>問題・正解の音声が正しく再生され、イラストも表示される</t>
+          <t>結果: 3つのステージすべてで、問題の音声（2回）と正解の音声が流れる。イラストも表示されている。</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr"/>
@@ -1042,22 +1262,24 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>「あと何問でクリア」の数が誤っている</t>
+          <t>結果画面の「あと何問でクリア」の数が間違っている</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>結果</t>
+          <t>ユーザーAでログインした状態</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>7問中4問正解で終える</t>
+          <t>① 好きなステージを最後までプレイする。
+② 結果画面で「Your Score」の正解数と「あと N 問正解でクリア！」の N を見る。
+③ 「5 −（正解数）＝ N」になっているか計算する。</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>「あと1問正解でクリア！」と表示される（5問でクリアのため）</t>
+          <t>結果: Nが計算と一致している（例: 4問正解なら「あと1問」）。以前のように7問中4問正解で「あと6問」のような誤りが出ない。</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr"/>
@@ -1076,22 +1298,25 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>時間切れ後に固まる</t>
+          <t>時間切れギリギリまで解いていると固まって進めなくなる</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>ゲーム</t>
+          <t>ユーザーAでログインし、マイクが使える状態</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>制限時間ぎりぎりまで問題を解き、時間切れさせる</t>
+          <t>① 好きなステージを開始し、2問目まで進める。
+② 残り時間が2〜3秒になるまで待ってから、マイクで何か答えを言う。
+③ そのまま時間切れになったあとの画面の動きを観察する。
+④ これを2〜3問で繰り返す。</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>固まらずに正解表示→次の問題へ進む</t>
+          <t>結果: 時間切れ後も固まらず、正解が表示されて次の問題に進む。</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr"/>
@@ -1110,22 +1335,23 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>ログインボタンの反応がわからない</t>
+          <t>ログインボタンを押しても反応がわからず何度も押してしまう</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>ログイン</t>
+          <t>Chromeでテスト用URLを開き、ユーザーAのID・パスワードを入力した状態</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>LOGINボタンを押す</t>
+          <t>① 「LOGIN」ボタンを1回押す。
+② ボタンの見た目の変化を観察する。</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>ボタンの表示が変わり、処理中であることがわかる</t>
+          <t>結果: ボタンが「Logging in...」に変わり、処理中であることが見てわかる。</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr"/>
@@ -1144,26 +1370,32 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>ログインに1分かかる</t>
+          <t>ログインに1分ほどかかる</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>ログイン</t>
+          <t>30分以上誰もシステムを使っていない状態（テスト初日の最初に実施するのがおすすめ）</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>しばらく（30分以上）誰も使っていない状態でログインする</t>
+          <t>① Chromeでテスト用URLを開き、すぐにユーザーAでログインする。
+② ログインに5秒以上かかる場合、ボタンの下に案内が出るか見る。
+③ 案内が出たら、そのまま待ってログインできるか確認する。</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>時間がかかる場合「サーバーを起動しています…」の案内が出る。案内どおり待つとログインできる</t>
+          <t>結果: 時間がかかる場合は「サーバーを起動しています… 最大1分ほどかかる場合があります。」の案内が表示され、待っているとログインできる。（すぐログインできた場合は、案内が出なくてもOKです）</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>時間条件つき</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1178,26 +1410,32 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>固まったときの復帰が遅い</t>
+          <t>固まったときの復帰画面が出るまでが遅い（30秒〜1分かかっていた）</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>ゲーム</t>
+          <t>ゲーム中に画面が固まった場合のみ実施</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>（発生した場合のみ）ゲームが固まったときの時間を計る</t>
+          <t>① ゲーム中に画面が20秒以上動かなくなったら、時計で時間を計る。
+② 復帰用の画面が出るまでの秒数をメモする。
+③ 「次の問題へ」を押して先へ進めるか確認する。</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>20秒ほどで「リトライ/次の問題へ/やめる」の画面が出る</t>
+          <t>結果: 固まってから20秒ほどで「画面が停止しました」の画面が出て、「リトライ」「次の問題へ」「やめる」の3つから選べる。「次の問題へ」で次に進める。</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>発生した場合のみ</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1212,22 +1450,24 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>readが過去形の発音になる</t>
+          <t>read が過去形（レッド）の発音になる</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>ゲーム</t>
+          <t>ユーザーAでログインし、音が聞こえる状態</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>1-39-2の2問目「I read this book.」の音声を聞く</t>
+          <t>① Grade「1」・Part「39」・Subpart「2」を開始する。
+② 2問目（I read this book.）の音声をよく聞く。
+③ 「read」の部分が「リード」と「レッド」のどちらに聞こえるかメモする。</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>「リード」（現在形）と発音される</t>
+          <t>結果: 「リード」（現在形の発音）と読み上げられる。</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
@@ -1246,26 +1486,32 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>認証が必要ですの意味がわからない</t>
+          <t>「認証が必要です」と出たとき、どうすればよいかわからない</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>全体</t>
+          <t>前日にログインしてChromeを開いたまま、24時間以上たった状態</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>1日以上あけてから、開いたままの画面で操作する</t>
+          <t>① 開いたままの画面で、どこでもよいのでボタンを押して操作する（例: ステージ選択画面の「Game Start」）。
+② 画面の動きとメッセージを確認する。
+③ 案内に従ってログインし直し、続きから遊べるか確認する。</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>「セッションの有効期限が切れました。ログインし直してください。」と表示されログイン画面に移動する</t>
+          <t>結果: 自動でログイン画面に戻り、「セッションの有効期限が切れました。ログインし直してください。」と表示される。ログインし直すと普通に遊べる。</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>時間条件つき（テスト期間中に1回実施）</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1280,26 +1526,31 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>翌日スタートを押すと承認が必要と言われ進めない</t>
+          <t>翌日にスタートを押すと「承認が必要」と言われ先に進めない</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>ステージ選択</t>
+          <t>No.139と同じ状態（前日ログインのまま24時間以上放置）</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>前日に開いたままの画面で「Game Start」を押す</t>
+          <t>① ステージ選択画面でステージを選び「Game Start」を押す。
+② 画面の動きを確認する。</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>自動でログイン画面に移動し、ログインし直すと続きから遊べる</t>
+          <t>結果: エラーで止まらず、自動でログイン画面に移動して案内が表示される。ログインし直すと続きから遊べる。</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>時間条件つき（No.139と同時に実施可）</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1314,22 +1565,24 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>イラストと問題文が重なる</t>
+          <t>中2の問題でイラストと問題文が重なる</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>ゲーム</t>
+          <t>ユーザーAでログインした状態</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>中2のイラストつき問題（例: 2-45-2）をプレイする</t>
+          <t>① Grade「2」・Part「45」・Subpart「2」を開始する。
+② 各問題で、問題文の文字とイラストが重なっていないか見る（時間切れ進行でよい）。
+③ ほかに中2のイラストつきステージを2〜3個選び、同じように確認する。</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>問題文とイラストが重ならない</t>
+          <t>結果: どの問題でも問題文（左側）とイラスト（右側）が重ならず、両方ともきちんと読める・見える。</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr"/>
@@ -1348,22 +1601,24 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>2-22-1-7/2-24-1-2のread発音</t>
+          <t>2-22-1の7問目と2-24-1の2問目で read が過去形の発音になる</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>ゲーム</t>
+          <t>ユーザーAでログインし、音が聞こえる状態</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>該当の問題の音声を聞く</t>
+          <t>① Grade「2」・Part「22」・Subpart「1」を開始し、7問目まで進める（時間切れ進行でよい）。
+② 7問目の音声の「read」の発音を聞く。
+③ 同様に Grade「2」・Part「24」・Subpart「1」の2問目の音声を聞く。</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>「リード」（現在形）と発音される</t>
+          <t>結果: どちらも「リード」（現在形）と読み上げられる。</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
@@ -1382,22 +1637,24 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>問題文の最初の音が聞こえない</t>
+          <t>2-47-2の1問目で、問題文の最初の音が聞こえない</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>ゲーム</t>
+          <t>ユーザーAでログインし、音が聞こえる状態</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>2-47-2の1問目の音声を聞く</t>
+          <t>① Grade「2」・Part「47」・Subpart「2」を開始する。
+② 1問目（お手本）の音声を最初から注意して聞く。
+③ 文の頭の単語が欠けずに聞こえるかメモする。</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>文の最初から欠けずに聞こえる</t>
+          <t>結果: 問題文が最初の単語から欠けずに聞こえる。</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr"/>
@@ -1416,22 +1673,24 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>3-8-2の追加とイラスト</t>
+          <t>3-8-1に3-8-2を追加してほしい・イラストも足したい</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>ステージ選択/ゲーム</t>
+          <t>ユーザーAでログインした状態</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>中3のパート8でサブパート2を選んでプレイする</t>
+          <t>① Grade「3」・Part「8」のSubpartプルダウンを開き、「2」があるか確認する。
+② Subpart「2」を選んで開始する。
+③ 8問すべてでイラストが表示されるか確認する（時間切れ進行でよい）。</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>3-8-2が選択でき、8問すべてにイラストが表示される</t>
+          <t>結果: 3-8-2が選択でき、8問すべてにイラストが表示される。</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
@@ -1450,22 +1709,24 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>回答条件が1度しか読まれない</t>
+          <t>3-18-1と3-19-1で、2回読まれるはずの音声が1回しか読まれない</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>ゲーム</t>
+          <t>ユーザーAでログインし、音が聞こえる状態</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>3-18-1、3-19-1をプレイし、問題音声の回数を数える</t>
+          <t>① Grade「3」・Part「18」・Subpart「1」を開始する。
+② 各問題で、問題文の音声が何回流れるか数える（時間切れ進行でよい）。
+③ 同様に Grade「3」・Part「19」・Subpart「1」でも数える。</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>各問題の問題文が毎回2回読み上げられる（※画面の回答条件は音声では読まれません）</t>
+          <t>結果: すべての問題で、問題文の音声が毎回2回ずつ流れる。※画面に表示される「Requirement（回答条件）」の日本語は音声では読まれません（これは元々の仕様です）。</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr"/>
@@ -1484,22 +1745,23 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>3-20-1-3の問題文が1回しか読まれない</t>
+          <t>3-20-1の3問目の問題文が1回しか読まれない</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>ゲーム</t>
+          <t>ユーザーAでログインし、音が聞こえる状態</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>3-20-1の3問目の音声を聞く</t>
+          <t>① Grade「3」・Part「20」・Subpart「1」を開始し、3問目まで進める。
+② 3問目の問題文の音声の回数を数える。</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>問題文が2回読み上げられる</t>
+          <t>結果: 3問目も音声が2回流れる。</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr"/>
@@ -1518,22 +1780,23 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>3-23-2が7問までしか読まれない</t>
+          <t>3-23-2の問題が7問目までしか読まれない</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>ゲーム</t>
+          <t>ユーザーAでログインした状態</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>3-23-2を最後までプレイする</t>
+          <t>① Grade「3」・Part「23」・Subpart「2」を開始する。
+② 何も答えなくてよいので最後までプレイし、画面左上の問題番号を確認する。</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>デモ+7問=8問すべて出題される</t>
+          <t>結果: 問題番号が8まで進み、8問すべてが出題されてから結果画面になる。</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr"/>
@@ -1552,22 +1815,24 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>3-24以降がNo Data</t>
+          <t>3-24以降が「No Data」となり問題が出ない</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>ステージ選択/ゲーム</t>
+          <t>ユーザーAでログインした状態</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>中3のパート24〜35を選んでプレイする</t>
+          <t>① Grade「3」・Part「24」・Subpart「1」を開始する。
+② 1問目が表示されたら「やめる」で戻る。
+③ 同じ要領で Part「25」〜「35」まで、それぞれSubpart「1」を順に開いて確認する。</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>すべてのパートで問題が表示される</t>
+          <t>結果: どのパートも「No Data」にならず、問題が表示される。</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr"/>
@@ -1586,26 +1851,32 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>3-34-2の答えが認識されづらい</t>
+          <t>3-34-2で答えが認識されづらい</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>ゲーム</t>
+          <t>ユーザーAでログインし、マイクが使える状態</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>3-34-2で「If she were a cat, she'd sleep all day.」のように短縮形でも答えてみる</t>
+          <t>① Grade「3」・Part「34」・Subpart「2」を開始する。
+② 2問目で銃のボタンを押し、正解の文を「短縮形」で言ってみる（例: If she were a cat, she'd sleep all day.）。
+③ 別の問題では、縮めない言い方（… she would sleep …）でも言ってみる。</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>短縮形でも正解になる（完全な言い方でも正解になる）</t>
+          <t>結果: 短縮した言い方でも、縮めない言い方でも正解になる。</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>マイク使用</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1615,31 +1886,38 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>6/3-1</t>
+          <t>6/3起票</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>1-1-1が認識されない（特に8番）</t>
+          <t>1-1-1で答えを認識してもらえない（特に8問目）</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>ゲーム</t>
+          <t>ユーザーAでログインし、マイクが使える状態</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>1-1-1で「I」「You」など1語の答えを言う。文で言ってしまってもよい</t>
+          <t>① Grade「1」・Part「1」・Subpart「1」を開始する。
+② 2問目以降、答えの単語だけ（例: You）をマイクに向かって言う。
+③ 認識されにくいときは、問題の英文ごと（例: You run fast.）言ってみる。
+④ 8問目まで同じように試す。</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>答えの単語が入っていれば正解になる</t>
+          <t>結果: 単語だけでも、文ごと言っても、答えの単語が入っていれば正解になる。8問目も正解できる。</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>マイク使用</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1649,68 +1927,39 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>6/3-2</t>
+          <t>6/3起票</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>readがレッドと発音される</t>
+          <t>readを「レッド」と発音する問題が5つ残っている</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>ゲーム</t>
+          <t>ユーザーAでログインし、音が聞こえる状態</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>1-46-2-2 / 2-38-2-2 / 2-41-2-8 / 2-42-1-7 / 2-47-1-7 の音声を聞く</t>
+          <t>① 次の5つの問題まで進め、それぞれ音声の「read」の発音を聞く（時間切れ進行でよい）。
+・Grade1・Part46・Subpart2 の 2問目
+・Grade2・Part38・Subpart2 の 2問目
+・Grade2・Part41・Subpart2 の 8問目
+・Grade2・Part42・Subpart1 の 7問目
+・Grade2・Part47・Subpart1 の 7問目</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>すべて「リード」（現在形）と発音される</t>
+          <t>結果: 5つすべてで「リード」（現在形）と読み上げられる。</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr"/>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>B-21</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>6/3-3</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>（同上・対象一覧の確認）</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>ゲーム</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>上記5問以外にreadを含む問題があれば音声を聞く</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>「リード」と発音される</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H22"/>
+  <autoFilter ref="A1:H21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/外注テスト項目書_2026-07-02.xlsx
+++ b/outputs/外注テスト項目書_2026-07-02.xlsx
@@ -1057,7 +1057,7 @@
       <c r="E14" s="5" t="inlineStr">
         <is>
           <t>① 「ユーザー情報」の表に生徒の一覧が表示されているか確認する。
-② どれか1人の「編集」を押す。
+② 「テスターB」の行の「編集」を押す（他のユーザーには触れないこと）。
 ③ 「解いている最新のパート」の数字を1つ変えて「保存」を押す。
 ④ 表の表示が変わったか確認する。
 ⑤ 同じ手順で元の数字に戻しておく。</t>

--- a/outputs/外注テスト項目書_2026-07-02.xlsx
+++ b/outputs/外注テスト項目書_2026-07-02.xlsx
@@ -974,7 +974,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>クリアできなくても10回挑戦すると次のステージへ進めること【時間がかかる項目・約40分】</t>
+          <t>クリアできなくても3回挑戦すると次のステージへ進めること【時間がかかる項目・約15分】</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -986,13 +986,13 @@
         <is>
           <t>① ユーザーBの現在のステージ（プルダウンで最後に出てくるステージ）を開始する。
 ② クリアせずに（答えなくてよい）最後までプレイする。※「やめる」で途中終了すると回数に数えられないので、必ず結果画面まで進めること。
-③ 「Retry」からもう一度同じステージをプレイする。これを合計10回繰り返す。
-④ 10回目の結果画面のあと、ステージ選択画面のプルダウンを確認する。</t>
+③ 「Retry」からもう一度同じステージをプレイする。これを合計3回繰り返す。
+④ 3回目の結果画面のあと、ステージ選択画面のプルダウンを確認する。</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>結果: 10回目が終わると、クリアしていなくても次のステージがプルダウンに追加されて選べるようになっている。</t>
+          <t>結果: 3回目が終わると、クリアしていなくても次のステージがプルダウンに追加されて選べるようになっている。</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>

--- a/outputs/外注テスト項目書_2026-07-02.xlsx
+++ b/outputs/外注テスト項目書_2026-07-02.xlsx
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -700,7 +700,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>結果: ①で「Ranking 👑」の画面に切り替わり、今月の期間（例: Period: 2026/07）と「Number of try」「Best Scores」の2つの表が表示されている。③でステージ選択画面に戻っている。</t>
+          <t>結果: ①で「Ranking 👑」の画面に切り替わり、今月の期間（例: Period: 2026/07）と「Tries」「Best Scores」の2つの表が表示されている。③でステージ選択画面に戻っている。</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr"/>
@@ -1022,7 +1022,7 @@
       <c r="E13" s="5" t="inlineStr">
         <is>
           <t>① ステージ選択画面の「Ranking 🏆」を押す。
-② 「Number of try」（挑戦回数）の表を見る。</t>
+② 「Tries」（挑戦回数）の表を見る。</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -1145,6 +1145,41 @@
       </c>
       <c r="G16" s="5" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>A-16</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>ゲーム画面</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>iPad(タブレット)でも音声が出て、声を認識できること</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>iPad(SafariまたはChrome)でテスト用URLを開き、ユーザーAでログインした状態</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>① ステージ選択画面から「Game Start」を押し、Requirement画面で「Start」を押す。
+② 問題文の読み上げ(音声)が聞こえるか確認する。
+③ ガンボタンを押してから問題の答えを話し、もう一度ガンボタンを押す。
+④ 「Heard:」に話した内容が表示されるか確認する。</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>結果: ②で音声が聞こえ、④で話した内容が表示される。音が出ない・認識されない場合はNGとして端末名とOSバージョンを備考に記入してください。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H16"/>
